--- a/src/attributions/attributions_ig_traj_399.xlsx
+++ b/src/attributions/attributions_ig_traj_399.xlsx
@@ -1568,46 +1568,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.001371844551513917</v>
+        <v>-0.02932456866911341</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08084566397295576</v>
+        <v>0.07414827574562335</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1623375701787226</v>
+        <v>-0.05798533228461811</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03383682830627161</v>
+        <v>0.06660751357486228</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03298545383821349</v>
+        <v>0.02005508027722371</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.07411632965920736</v>
+        <v>-0.03614599852357066</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1619,49 +1619,49 @@
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02194285100934563</v>
+        <v>-0.02176965293999829</v>
       </c>
       <c r="T3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04111272864562551</v>
+        <v>0.03856929417052058</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1484208584342681</v>
+        <v>-0.06917447918417849</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
         <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1228947243220097</v>
+        <v>0.05361720264656603</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.02027652769946839</v>
+        <v>-0.05531121616113956</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.005471669933826952</v>
+        <v>-0.03511587849643803</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1673,28 +1673,28 @@
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.03524849510865018</v>
+        <v>0.009956328404628742</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.03906716111421538</v>
+        <v>-0.05471696640099349</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.2010344840329339</v>
+        <v>-0.08354634678730738</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1703,79 +1703,79 @@
         <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.004491044258886878</v>
+        <v>-0.08338651304138282</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2126223527323602</v>
+        <v>0.02331385142782934</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1147962699715393</v>
+        <v>-0.2230810967883338</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.001992879861097481</v>
+        <v>-0.01156504193986379</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.03887207008373938</v>
+        <v>0.01195023773952047</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.03811583492091791</v>
+        <v>0.03545753049098961</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.04325487604503384</v>
+        <v>0.06193869662251676</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.03758600498840801</v>
+        <v>0.00126982993930673</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.2908140658679297</v>
+        <v>0.02471640074949305</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,19 +1784,19 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.1234512319265342</v>
+        <v>-0.1060308577242953</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1784307876259955</v>
+        <v>0.1169505722991437</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.1143442736784246</v>
+        <v>-0.1183078334547538</v>
       </c>
       <c r="BZ3" t="n">
         <v>-0</v>
@@ -1805,52 +1805,52 @@
         <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.01725534963622691</v>
+        <v>0.06025958265800779</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.02478518635721767</v>
+        <v>-0.02333662268922768</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.07669232146173705</v>
+        <v>0.07118321134769084</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.009038840622859147</v>
+        <v>-0.03516558944836323</v>
       </c>
       <c r="CN3" t="n">
         <v>-0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.06142075721626292</v>
+        <v>0.001726658585503376</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.2425066523752913</v>
+        <v>-0.03642055832460018</v>
       </c>
       <c r="CR3" t="n">
         <v>-0</v>
@@ -1859,52 +1859,52 @@
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.01000753083961489</v>
+        <v>0.04773414456318027</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.0133524500961113</v>
+        <v>-0.04082913081419104</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.05126530295756766</v>
+        <v>0.02964472108496569</v>
       </c>
       <c r="DA3" t="n">
         <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-4.187246485248019e-05</v>
+        <v>0.04316281490833195</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.0006006283547799425</v>
+        <v>0.0005733183108955193</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.04628011692119417</v>
+        <v>0.1495481280432165</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
@@ -1913,82 +1913,82 @@
         <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.02623768187614814</v>
+        <v>0.08666608917426946</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.0591414656221296</v>
+        <v>0.03033936780051052</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2009938105648152</v>
+        <v>-0.1023128098741615</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.05846849947681972</v>
+        <v>0.02299641289459597</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.004632907566327422</v>
+        <v>0.1415745183488388</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.07228553381688745</v>
+        <v>-0.09156885093254735</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0147212612554277</v>
+        <v>0.03337134565786414</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.05388109922033293</v>
+        <v>0.01230474701367673</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.02845847340722513</v>
+        <v>0.06593781538316944</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
@@ -1997,28 +1997,28 @@
         <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.0115411263590276</v>
+        <v>0.01339141506424083</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.001935906204714263</v>
+        <v>-0.0158605262903135</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.00848492606286017</v>
+        <v>0.1037937552831838</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
         <v>0</v>
@@ -2027,25 +2027,25 @@
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.02697514017038416</v>
+        <v>0.04615133081291098</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.01974407059717151</v>
+        <v>-0.03996581820224639</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.03700298383870756</v>
+        <v>0.04433260773809322</v>
       </c>
       <c r="FC3" t="n">
         <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2054,46 +2054,46 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.07268200976672015</v>
+        <v>0.1743438904201151</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.04379072490926807</v>
+        <v>0.03394516391973104</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.06585930436866774</v>
+        <v>-0.004511383743468097</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN3" t="n">
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.06641274536686821</v>
+        <v>0.138102831603068</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.0005780353702028195</v>
+        <v>0.001635553661145954</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.00744908376286422</v>
+        <v>0.007030669588395579</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2108,13 +2108,13 @@
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.05441835570111056</v>
+        <v>0.1436778740373033</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.04189194063083341</v>
+        <v>3.485796525936236e-05</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
@@ -2123,13 +2123,13 @@
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>0</v>
@@ -2140,16 +2140,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2381201665541946</v>
+        <v>0.1428662640808493</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.04660248287895071</v>
+        <v>-0.03493270793663175</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0454361305462846</v>
+        <v>-0.01674956265614259</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,25 +2161,25 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09833848807106792</v>
+        <v>0.0891838298590516</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0328561514835848</v>
+        <v>0.03120038805752369</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.03075081865024878</v>
+        <v>-0.0114086847196038</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -2188,85 +2188,85 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1340484497763859</v>
+        <v>0.036648652284359</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03826554725061516</v>
+        <v>-0.03472657286140333</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03644409189812885</v>
+        <v>-0.02774067586627074</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0393439570601165</v>
+        <v>-0.01500344603453358</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.02288864598545243</v>
+        <v>-0.03541296920728237</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.02453797588788951</v>
+        <v>-0.05095719008260625</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.05839249441883342</v>
+        <v>0.08196965459232154</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.0356983978332959</v>
+        <v>-0.03817217814702827</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01061319676085611</v>
+        <v>0.03840479976828661</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,25 +2275,25 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3934837790153493</v>
+        <v>0.1982625689165675</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.007187235688812259</v>
+        <v>-0.04422461993649853</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1764934815249821</v>
+        <v>-0.07139552400801573</v>
       </c>
       <c r="AY4" t="n">
         <v>-0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01084149016269325</v>
+        <v>-0.01465449214311359</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.04005858503499517</v>
+        <v>-0.01086882027651521</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.06443481074443812</v>
+        <v>-0.01421901367776853</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.04551464302100783</v>
+        <v>-0.008908367517630481</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.09875463572826514</v>
+        <v>0.02272322990026539</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.01664732272162753</v>
+        <v>0.05564845452929572</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,25 +2356,25 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.2426099436166873</v>
+        <v>0.162664904898247</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01488846852064759</v>
+        <v>-0.04828567599242326</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.006288186796209152</v>
+        <v>-0.002890999978403574</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2383,46 +2383,46 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.07226791950900879</v>
+        <v>-0.0794300814569404</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.01394967872563933</v>
+        <v>0.0629319262873039</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.02564647996567193</v>
+        <v>0.00028284798893664</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.0424043870403043</v>
+        <v>-0.05535622943965447</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.1140490399216899</v>
+        <v>0.08205708106135336</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1757243162206194</v>
+        <v>0.03752949385139499</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2437,49 +2437,49 @@
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.05683567922241931</v>
+        <v>-0.08358491482747138</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.04409763680267578</v>
+        <v>0.06910627455054834</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.01934477291433704</v>
+        <v>0.006845690285960293</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.07856949220064104</v>
+        <v>-0.02868770786050985</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.0056782525123841</v>
+        <v>-0.004358081558137914</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0002442847854030615</v>
+        <v>0.00124359555333452</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,25 +2491,25 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.07350961093172279</v>
+        <v>-0.05171746875421085</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.04320206265762377</v>
+        <v>0.02900102434205458</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.00684255266044714</v>
+        <v>-0.04783635296754358</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,52 +2518,52 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.06130238256566233</v>
+        <v>0.0176236954827589</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.07655884876029197</v>
+        <v>0.03806737731970915</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.02401909414745763</v>
+        <v>-0.007331125251659685</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.0356188774424391</v>
+        <v>-0.05356821420447027</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.07738099570011496</v>
+        <v>0.04942146556851415</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.003560667028352124</v>
+        <v>0.01110506661554842</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
@@ -2572,73 +2572,73 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.04261031724786267</v>
+        <v>-0.04683222535116727</v>
       </c>
       <c r="EQ4" t="n">
         <v>0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.03606552368534391</v>
+        <v>-0.03915811847407025</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.02902247283096973</v>
+        <v>0.005176522507115714</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.06536109702638261</v>
+        <v>-0.09085947617470333</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.02171715821057696</v>
+        <v>0.0654931129038135</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.0396523841928353</v>
+        <v>-0.001539987883948824</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.03195631732973755</v>
+        <v>-0.04544014181261237</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.05454445886291195</v>
+        <v>0.01979290234186749</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.0186053576186381</v>
+        <v>0.006565852677769611</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,61 +2647,61 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.001580264756750093</v>
+        <v>0.001197327111656891</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.009068442961292363</v>
+        <v>0.09773948696865975</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.000519532962706345</v>
+        <v>-0.0003832838068290397</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX4" t="n">
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.00597220835810917</v>
+        <v>-0.06553692736384222</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.02251976247453349</v>
+        <v>0.01922308189376969</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03460886308513484</v>
+        <v>0.32699448622058</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03020759073766605</v>
+        <v>0.07117769185507136</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02365603247346672</v>
+        <v>-0.1713689969705457</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,34 +2736,34 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009542425661361835</v>
+        <v>0.2375306068017008</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0161367058351552</v>
+        <v>-0.01431495978477833</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.003041601678026334</v>
+        <v>-0.02542662833973389</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.003831205861613085</v>
+        <v>0.1519091154220585</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2772,13 +2772,13 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01625853525482892</v>
+        <v>-0.1093282707048072</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01787019890323363</v>
+        <v>0.01882901781062636</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
@@ -2790,19 +2790,19 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01218818185706404</v>
+        <v>-0.07199355691015506</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.008701506208501783</v>
+        <v>-0.2029873809881877</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00783300294628521</v>
+        <v>-0.01636575352379565</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2811,13 +2811,13 @@
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.007179704352285293</v>
+        <v>0.1197740024980357</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,37 +2826,37 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01304148640509266</v>
+        <v>0.1002540727004206</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.005593364405496178</v>
+        <v>-0.09239690287177427</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.04156048822075047</v>
+        <v>0.4586260985362741</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.03370476922286599</v>
+        <v>-0.1571118647079414</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01198628329646662</v>
+        <v>-0.2076800478789768</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2865,13 +2865,13 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01185718763188487</v>
+        <v>0.003381207368910602</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.009871291576804893</v>
+        <v>-0.03297636113728955</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.007229601603989739</v>
+        <v>-0.0365921820437878</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,28 +2895,28 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03263609798423175</v>
+        <v>0.03121435175896399</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01358633649816978</v>
+        <v>0.0903551240043558</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.006390627747771129</v>
+        <v>0.1217085469476658</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.01881540969826801</v>
+        <v>0.4574384571693261</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,37 +2934,37 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.02226177537394018</v>
+        <v>0.02191667589831649</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.005646056456629951</v>
+        <v>-0.1312699488579551</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.00435139998628192</v>
+        <v>-0.1596010785056929</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01130999517519279</v>
+        <v>-0.0669314773619898</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01289128439401718</v>
+        <v>0.1332785409090528</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
@@ -2976,55 +2976,55 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.001758697686727941</v>
+        <v>-0.1890097978197441</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.002035708194445502</v>
+        <v>0.08863883096575956</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.002783648472739853</v>
+        <v>0.06854060164001716</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0009473385810425005</v>
+        <v>-0.1422097765171225</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01081140772135513</v>
+        <v>-0.06331447193795536</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.01706865097824643</v>
+        <v>0.1342524761118655</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.01088612556695604</v>
+        <v>-0.07643001038014827</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01305745338351002</v>
+        <v>-0.1066763891221192</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.0009412070168228854</v>
+        <v>0.01355754562749646</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,31 +3054,31 @@
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.007756728056583619</v>
+        <v>-0.1037870526380777</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01833054939225521</v>
+        <v>0.02506288144958006</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.01062240331372217</v>
+        <v>0.0156789190592001</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,25 +3087,25 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.01164291937119425</v>
+        <v>0.01671831827466253</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01556957266174333</v>
+        <v>-0.01718643931947645</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.005425173041945866</v>
+        <v>0.1521286360126074</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,34 +3114,34 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0006988116594100074</v>
+        <v>-0.02446521643575058</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.00693455990120736</v>
+        <v>-0.1408634992677789</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01383602046981935</v>
+        <v>0.04776942329004912</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0074880182267768</v>
+        <v>-0.07465549884033551</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,25 +3150,25 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02288007840437774</v>
+        <v>-0.2427100198898671</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.01051919505171992</v>
+        <v>0.09274628192209215</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.003295960628571619</v>
+        <v>-0.1681925174377023</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,10 +3177,10 @@
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01059235575589497</v>
+        <v>-0.09741526820712849</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01580119949853777</v>
+        <v>0.1062061258609329</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
@@ -3195,34 +3195,34 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.01395721333022275</v>
+        <v>-0.1588214428398568</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02787634802646007</v>
+        <v>0.07044393006754351</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01337002332781242</v>
+        <v>0.1075323229563659</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.002263515124052133</v>
+        <v>0.02821115704971663</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
@@ -3231,25 +3231,25 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0002964308878237977</v>
+        <v>0.002150114707640018</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.01903245909829185</v>
+        <v>-0.04344759079573444</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01674710119394415</v>
+        <v>-0.06334639698707648</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.001227307742384806</v>
+        <v>0.07530528572435921</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9220014565960145</v>
+        <v>0.2030912372127469</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2778947716155181</v>
+        <v>-0.07950967465353065</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.09559957651461831</v>
+        <v>-0.02891463758125387</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,25 +3868,25 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4778928171855836</v>
+        <v>0.1736685376328475</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07360059191997388</v>
+        <v>-0.03076308076988111</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1341561329036953</v>
+        <v>-0.04068768702505852</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
         <v>-0</v>
@@ -3898,52 +3898,52 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2214092877968034</v>
+        <v>0.05095807912369978</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.129072678976378</v>
+        <v>-0.04213297882895106</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.06508477817575173</v>
+        <v>-0.0500463177330906</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1785511686372633</v>
+        <v>-0.02383516954847797</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.06137524030792538</v>
+        <v>-0.03807689959762772</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02509176398195724</v>
+        <v>-0.07363275024952849</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
@@ -3955,22 +3955,22 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.1453002302971834</v>
+        <v>0.09985253394172465</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.08935523384943357</v>
+        <v>-0.04401558196840386</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.07466322243171404</v>
+        <v>0.03227379832654732</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.007585776942485</v>
+        <v>0.236240664515062</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0683176473369968</v>
+        <v>-0.07317762893305259</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.2857306226620417</v>
+        <v>-0.1025468625911203</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.1014203332606681</v>
+        <v>-0.03041094097131651</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.06971776995120639</v>
+        <v>-0.01270854668769239</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.2343080335216328</v>
+        <v>-0.0236380560202591</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1278369354274551</v>
+        <v>0.002962522210822858</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.2555357983653837</v>
+        <v>0.02433706616450397</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.09185191757940524</v>
+        <v>0.05964844359462038</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,25 +4063,25 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.57486911629128</v>
+        <v>0.1926379505419185</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.04057403630709411</v>
+        <v>-0.04794926860287445</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.0139829220440828</v>
+        <v>-0.03547514902826494</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4090,46 +4090,46 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.2459400149240399</v>
+        <v>-0.08999179466508959</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.05308936099492181</v>
+        <v>0.07619941292432966</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.07713474548619015</v>
+        <v>0.008454010690127954</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.03175271161283606</v>
+        <v>-0.05956727244946249</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.285876520948549</v>
+        <v>0.1220365925304995</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.2666672895273893</v>
+        <v>0.05254601576609024</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4144,49 +4144,49 @@
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1959311595867471</v>
+        <v>-0.08986775343093144</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.1364950315289026</v>
+        <v>0.08400148340606406</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.07074147342153365</v>
+        <v>0.01414093329027434</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.07615769232795752</v>
+        <v>-0.03588346633891551</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.02415908815951241</v>
+        <v>-0.006220772644888912</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01656724529863366</v>
+        <v>-0.01173929675023407</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -4198,22 +4198,22 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.1272425473031062</v>
+        <v>-0.05625220986831545</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.07493542301293402</v>
+        <v>0.008502215185156448</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.03857877477754681</v>
+        <v>-0.03274706910644239</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
@@ -4225,16 +4225,16 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.03437391791093696</v>
+        <v>0.01606242562861328</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.109249538171649</v>
+        <v>0.03198602383358137</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.145318594681462</v>
+        <v>-1.134981728063302e-05</v>
       </c>
       <c r="EB7" t="n">
         <v>-0</v>
@@ -4252,49 +4252,49 @@
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1142249821274946</v>
+        <v>-0.06082748908067473</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.07610910484780273</v>
+        <v>0.08064490777786081</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.006520436317959151</v>
+        <v>0.007698678332677224</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.1913408224767314</v>
+        <v>-0.04586484101115493</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.1349227740066157</v>
+        <v>-0.0592356295814746</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.1553088349266127</v>
+        <v>0.004479027753637448</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,46 +4306,46 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.2120907018754543</v>
+        <v>-0.1006019033314629</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.089214261498473</v>
+        <v>0.08144490221067049</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.08147209820082689</v>
+        <v>0.0006316057042513953</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.04708975182714379</v>
+        <v>-0.05703249057997436</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1549558471802119</v>
+        <v>0.04131233458709305</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.046871773896155</v>
+        <v>0.006195938549818499</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
@@ -4354,25 +4354,25 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.03113295124100276</v>
+        <v>0.001341817177647018</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.1124558661267754</v>
+        <v>0.112284424681618</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.0894494300831689</v>
+        <v>-0.007964354722752842</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4384,31 +4384,31 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.0806453017107039</v>
+        <v>-0.07582508147411393</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.06718955160958243</v>
+        <v>0.03436692715541297</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4985,25 +4985,25 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.08570394655204752</v>
+        <v>0.3000558389091768</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.004762174097094509</v>
+        <v>0.008207703201033742</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.02961833794888943</v>
+        <v>-0.1401666786220813</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02924264110628583</v>
+        <v>0.3049360742976698</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,79 +5021,79 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01739032445875397</v>
+        <v>-0.07089838699396915</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.00171657446348376</v>
+        <v>-0.006387355114776478</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.001873096068095288</v>
+        <v>0.1274587059152064</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.005628147889032029</v>
+        <v>-0.003321877622111196</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01660323204839247</v>
+        <v>0.05141344878238131</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.02067962637068243</v>
+        <v>-0.01401547968451335</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02550400116321969</v>
+        <v>-0.1372003103165305</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.006934459581603959</v>
+        <v>0.04272799772157299</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
         <v>-0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01415472158585814</v>
+        <v>0.1249859297047884</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -5102,52 +5102,52 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.009751919972095093</v>
+        <v>0.01644921563284165</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.0143844363272716</v>
+        <v>-0.08172024169956464</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.08939622249811574</v>
+        <v>0.3437925139815031</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.01107356736227258</v>
+        <v>-0.1966135961345971</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.01205724363012216</v>
+        <v>-0.1998147232075583</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01823576958225126</v>
+        <v>-0.005834056272222597</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,25 +5156,25 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.01816550672536588</v>
+        <v>-0.06898557751674876</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.008555819791448899</v>
+        <v>-0.02233429455647211</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0388842384491306</v>
+        <v>0.009237765446187211</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,10 +5183,10 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.03097846658137151</v>
+        <v>0.09430594273815504</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.007507645210629653</v>
+        <v>0.06533679989652434</v>
       </c>
       <c r="BR9" t="n">
         <v>-0</v>
@@ -5195,28 +5195,28 @@
         <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.03784207187519049</v>
+        <v>0.2905291355469086</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.01490092246967766</v>
+        <v>-0.00193580780991584</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.02511682159198671</v>
+        <v>-0.06669637998818802</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>-0</v>
@@ -5228,22 +5228,22 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.01008039226872271</v>
+        <v>-0.1251292910002886</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.002722696655871586</v>
+        <v>0.01435538011349288</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0151426166205462</v>
+        <v>0.08535169196250343</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5252,37 +5252,37 @@
         <v>-0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.01175768104221819</v>
+        <v>-0.1267324220394873</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001405722380909167</v>
+        <v>0.2484923976160915</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.03573666324852157</v>
+        <v>0.008251290021180149</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.0040684016751126</v>
+        <v>-0.1138882191527022</v>
       </c>
       <c r="CX9" t="n">
         <v>0</v>
@@ -5291,67 +5291,67 @@
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.00231358940861706</v>
+        <v>0.01600818308430163</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.01742391690982365</v>
+        <v>0.09627724605943863</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.003949953206948558</v>
+        <v>-0.0946125829754198</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
         <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02745415096121482</v>
+        <v>-0.07366418216038535</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01838663058192442</v>
+        <v>0.1160738929052213</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.01176881754091003</v>
+        <v>-0.09449112563061468</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.01906123439975049</v>
+        <v>-0.04150151813948108</v>
       </c>
       <c r="DS9" t="n">
-        <v>-6.255685713563299e-05</v>
+        <v>0.00131715797162527</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,25 +5363,25 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.03356658264065009</v>
+        <v>0.009404308614185135</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.04456386142514099</v>
+        <v>-0.07383327804249086</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.0142310128957808</v>
+        <v>0.04061178134789597</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,76 +5390,76 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.002890611388814356</v>
+        <v>-0.01120463059442342</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.005204684124027757</v>
+        <v>-0.03446345636668081</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0007211932348093666</v>
+        <v>0.0158750133684658</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.002891195786095624</v>
+        <v>-0.06508484513096995</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.0224055395843075</v>
+        <v>-0.1588951190350346</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.05206023078482194</v>
+        <v>-0.1367992460674707</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001800042758800274</v>
+        <v>-0.1346492676525104</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.002231583772566117</v>
+        <v>0.001879227522018264</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.01878619840872086</v>
+        <v>0.07393774913719159</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5468,37 +5468,37 @@
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02662077208899953</v>
+        <v>-0.1147688624747824</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.04487320654000536</v>
+        <v>0.1335224081307978</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.001162484106135798</v>
+        <v>0.09274189317682006</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.005503640204874609</v>
+        <v>0.01138696919004034</v>
       </c>
       <c r="FR9" t="n">
         <v>0</v>
@@ -5507,25 +5507,25 @@
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.01375540401250621</v>
+        <v>-0.0463225059491579</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.03552260390470823</v>
+        <v>-0.09531768489416126</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02774419364632078</v>
+        <v>-0.05573927187573727</v>
       </c>
       <c r="GA9" t="n">
         <v>0</v>
@@ -5537,13 +5537,13 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.00839698709238863</v>
+        <v>0.02114856037198263</v>
       </c>
       <c r="GE9" t="n">
         <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2833546286738226</v>
+        <v>0.3289570857582715</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.101592918171183</v>
+        <v>-0.108163506843854</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.07828584957099639</v>
+        <v>-0.01850017816742568</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5575,112 +5575,112 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.175840782320278</v>
+        <v>0.3102262762194405</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.05602785981638386</v>
+        <v>-0.07692365780968757</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1048957704953753</v>
+        <v>-0.05231541851229724</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.07022290279615392</v>
+        <v>0.07818421826614685</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01112837803677517</v>
+        <v>-0.05392827137723356</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03056978923561534</v>
+        <v>-0.05582537838431175</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.06357975970496098</v>
+        <v>-0.06369751051341938</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.03374096208081235</v>
+        <v>-0.06514035846729212</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.001373485987285105</v>
+        <v>-0.09621406875628516</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02690771333750823</v>
+        <v>0.1315310942635237</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.03910269674382059</v>
+        <v>-0.0739863827310589</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.07197715897299557</v>
+        <v>0.04277927237945187</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,16 +5689,16 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3386387861532482</v>
+        <v>0.3109149994760884</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.0214424891413207</v>
+        <v>-0.1200565313215068</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1139089360061006</v>
+        <v>-0.1598431936181242</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01891126431104804</v>
+        <v>-0.05798014830070108</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.0391658876479334</v>
+        <v>0.009570392154069546</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1138339961744595</v>
+        <v>-0.03549700151951395</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5743,22 +5743,22 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0956037555070904</v>
+        <v>-0.0009280501319610726</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.07075030787540444</v>
+        <v>0.02294064869168851</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1088760606692217</v>
+        <v>0.04833197799555562</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,19 +5770,19 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1798341851604117</v>
+        <v>0.2794402531974943</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.005293176254969873</v>
+        <v>-0.1272073237380466</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.03083261787321953</v>
+        <v>-0.05461267204841929</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5791,28 +5791,28 @@
         <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.06253279497427035</v>
+        <v>-0.1282870420792791</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.007485216739666451</v>
+        <v>0.1082465202174531</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.004349524878456553</v>
+        <v>0.006154098341823311</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
@@ -5821,25 +5821,25 @@
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.05050663905422759</v>
+        <v>-0.08766328493207963</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.09244376485940768</v>
+        <v>0.1851098576159783</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.09559192036448076</v>
+        <v>0.1048551506871356</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
         <v>-0</v>
@@ -5851,25 +5851,25 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.03994324891788106</v>
+        <v>-0.1220932188270763</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.02781910925677175</v>
+        <v>0.1224502012558847</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.006755827615596095</v>
+        <v>0.009131763890818035</v>
       </c>
       <c r="DA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
@@ -5878,22 +5878,22 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.01260420671892936</v>
+        <v>-0.1249469560268903</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.008895758249934207</v>
+        <v>0.05956536307464182</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.01921513515360837</v>
+        <v>-0.06703131208357022</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5905,76 +5905,76 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.06320730251582594</v>
+        <v>-0.05452018375766399</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.05839930640913195</v>
+        <v>0.03122342959661827</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.0009959059793029875</v>
+        <v>-0.01190669339438248</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.02987837793026343</v>
+        <v>0.03941395272433253</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.03899126815159416</v>
+        <v>0.005207250601766305</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.01405375221085923</v>
+        <v>-0.01829592705302498</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02038639705360021</v>
+        <v>-0.08760771455710743</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.07877080679412624</v>
+        <v>0.1138765520368604</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04417841051609474</v>
+        <v>0.007996054013261922</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
@@ -5983,25 +5983,25 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.05231512008821688</v>
+        <v>-0.07470728385440906</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.04554248992468066</v>
+        <v>-0.08278297622838307</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01554087327171749</v>
+        <v>-0.01419494778083719</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
@@ -6013,73 +6013,73 @@
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.04929368816855415</v>
+        <v>-0.1348486030838537</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.02047144966939845</v>
+        <v>0.1197472433108389</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01798717823996143</v>
+        <v>-0.003174640575557124</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.04067764435631707</v>
+        <v>-0.07478952819906337</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0569145997504086</v>
+        <v>0.09629892804683873</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.01370042885716283</v>
+        <v>-0.03168065239817841</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.006559856081812816</v>
+        <v>0.01018902778901834</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.01488170742817292</v>
+        <v>0.1005613216782031</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0370520071993499</v>
+        <v>0.001731976635255825</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
@@ -6091,31 +6091,31 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.01296508433677085</v>
+        <v>-0.1213547325971489</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.02733010770851524</v>
+        <v>0.06859060264736259</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6689,46 +6689,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2762252416738939</v>
+        <v>0.1091119523947085</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.02988091522559826</v>
+        <v>-0.02794909901661538</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.05023935493558282</v>
+        <v>-0.03717027843653702</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.143048108030468</v>
+        <v>0.1063301976575252</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01349544006219884</v>
+        <v>-0.01724178108647475</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05387329518898853</v>
+        <v>-0.04872550298061012</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6740,25 +6740,25 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04939501435335723</v>
+        <v>0.0291528817677714</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.02038036977198033</v>
+        <v>-0.006379489252536302</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04088070515652634</v>
+        <v>-0.004008559445620719</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,46 +6770,46 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.04798793074168704</v>
+        <v>-0.01186696125472293</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.0125863115642732</v>
+        <v>-0.03573810465326596</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.008091239377812641</v>
+        <v>-0.049803961155602</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.01427636085149869</v>
+        <v>0.04241200422126846</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.01477575277899975</v>
+        <v>-0.002885327289710234</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.04232470563602584</v>
+        <v>0.03974601336485168</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6827,25 +6827,25 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2508923507889798</v>
+        <v>0.1167031627670048</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02876335495707849</v>
+        <v>-0.00333214583001796</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.05384870401972781</v>
+        <v>-0.06277498187313611</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,25 +6854,25 @@
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.04304081534367396</v>
+        <v>-0.03259195818125172</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.05727969440138</v>
+        <v>-0.008961726862334167</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.05495134102118232</v>
+        <v>-0.01435638157583532</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,19 +6881,19 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1167006007723582</v>
+        <v>0.02448289455751858</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.02398345452974286</v>
+        <v>0.01511688808594725</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.09865390734347176</v>
+        <v>0.05119319837009094</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6905,28 +6905,28 @@
         <v>-0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1467429892704941</v>
+        <v>0.1098968921436958</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.02767218571969798</v>
+        <v>-0.0310639569527285</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.02566301423888356</v>
+        <v>-0.01001104393751528</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,49 +6935,49 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.05612390633133235</v>
+        <v>-0.03539385425693255</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.006316730715198187</v>
+        <v>0.03054781176130237</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.004681924624143619</v>
+        <v>0.01772442163940743</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.0578103291166698</v>
+        <v>-0.04799240562094578</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.04462073924688541</v>
+        <v>0.0291191847892103</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.06634859720165377</v>
+        <v>0.02713715874345974</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,19 +6986,19 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.03545366890398363</v>
+        <v>-0.03323247568651461</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.008346286014633972</v>
+        <v>0.03346436503974594</v>
       </c>
       <c r="CZ12" t="n">
-        <v>9.170166046191923e-05</v>
+        <v>0.02055084263187124</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7016,22 +7016,22 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.009291133487398998</v>
+        <v>-0.0003356160205058436</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.05919675354919952</v>
+        <v>0.009081545649474505</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.007201546123536152</v>
+        <v>-0.004833722841705993</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7043,46 +7043,46 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.063466870541319</v>
+        <v>-0.03419025109117375</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.0007989199810870257</v>
+        <v>-0.01615118526452957</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01911245686312148</v>
+        <v>-0.0135847594528035</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.00381230000142832</v>
+        <v>0.03636952938372533</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.009026750249685482</v>
+        <v>0.01897485298609056</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.0261859912152989</v>
+        <v>-0.05023290117164281</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
@@ -7091,22 +7091,22 @@
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.0252694031643294</v>
+        <v>0.006827580213634018</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0.001898592101170465</v>
+        <v>0.01994164665152847</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.05102767659473094</v>
+        <v>0.03907948482747511</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
@@ -7115,7 +7115,7 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,25 +7124,25 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.02484206517393921</v>
+        <v>-0.02639214945737438</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.002853241946450607</v>
+        <v>0.03598805302233752</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02547876668166824</v>
+        <v>-0.008548993720469217</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
@@ -7151,16 +7151,16 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.03464195418179657</v>
+        <v>-0.04019852794924936</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0002958823973212805</v>
+        <v>0.03927864527350492</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.01398241447187081</v>
+        <v>0.01130167652560055</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7169,25 +7169,25 @@
         <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.008169320215385911</v>
+        <v>-0.002080761706031762</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.01821149048770684</v>
+        <v>0.0014349227035878</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.03041852253899668</v>
+        <v>-0.01924376708324746</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,34 +7196,34 @@
         <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.03631098310843467</v>
+        <v>0.01655963185276106</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.02582875069456097</v>
+        <v>0.04402547785347532</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.004858180666787133</v>
+        <v>-0.04524299666351685</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
@@ -7232,19 +7232,19 @@
         <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.002242319216275237</v>
+        <v>-0.01475391157590019</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.02656567340893892</v>
+        <v>0.00152709760194957</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2238815771624307</v>
+        <v>0.128967796086065</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0004178124418767925</v>
+        <v>-0.0272282407218616</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1401281384994044</v>
+        <v>-0.1010498386080638</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7285,28 +7285,28 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1525507066313521</v>
+        <v>0.2481455360581863</v>
       </c>
       <c r="L13" t="n">
         <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.01676812223351809</v>
+        <v>-0.07788249712743439</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1109883377759376</v>
+        <v>-0.1023269524086463</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,46 +7315,46 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01604090620744128</v>
+        <v>0.06451777447525629</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01322940629374845</v>
+        <v>-0.04675072401154424</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.005229082238178832</v>
+        <v>-0.003128909932539518</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.02872939884146045</v>
+        <v>-0.02537392976023215</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01652132666449051</v>
+        <v>-0.1264827011808843</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.008871304328551073</v>
+        <v>-0.01552090650567058</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,28 +7363,28 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.009326157404491785</v>
+        <v>0.02843066488412745</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01872370810112973</v>
+        <v>-0.001644557797650911</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.04231064350821406</v>
+        <v>-0.02524397402025807</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,37 +7393,37 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1539435205954069</v>
+        <v>0.2598029981100358</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.001163824199992763</v>
+        <v>-0.1049691276105686</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.06637165207244131</v>
+        <v>-0.08259408285663987</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.07038658543880516</v>
+        <v>-0.05666001319673326</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.03634243292216048</v>
+        <v>-0.06541458372373063</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.05937618712670126</v>
+        <v>-0.03043156102597485</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.07047877781091035</v>
+        <v>0.1002279102159762</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -7459,16 +7459,16 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.04690402964286691</v>
+        <v>0.05759608671903544</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0102095025138908</v>
+        <v>-0.006092092404131501</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
         <v>0</v>
@@ -7477,19 +7477,19 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.07974364052110731</v>
+        <v>0.2074298296775336</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.01432197699091665</v>
+        <v>-0.03916019702901401</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.01447388254460476</v>
+        <v>-0.03895386876466391</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,25 +7498,25 @@
         <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD13" t="n">
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.04443681172883662</v>
+        <v>-0.04415509326728419</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.0080721638974475</v>
+        <v>0.03298711047780354</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.03309475031446531</v>
+        <v>0.04587594364957318</v>
       </c>
       <c r="CJ13" t="n">
         <v>-0</v>
@@ -7525,40 +7525,40 @@
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.03046734119778527</v>
+        <v>-0.1626594753385011</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01926597158254763</v>
+        <v>0.1265169606341424</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01904617424061479</v>
+        <v>0.06335658838713672</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.02917230833885807</v>
+        <v>-0.03544282699698235</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
@@ -7567,10 +7567,10 @@
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.007466303756701008</v>
+        <v>0.01903742119313826</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.03139321846200504</v>
+        <v>0.05018440069677339</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7582,91 +7582,91 @@
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.01316276236747196</v>
+        <v>0.01067204744236048</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.002051309423804777</v>
+        <v>-0.02530028925210772</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.004126722499807811</v>
+        <v>0.001691115373819032</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.03014455734280325</v>
+        <v>-0.07099098047174451</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01083342570399731</v>
+        <v>0.04688633122966532</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.01290346142683257</v>
+        <v>-0.005456258435178134</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.0008743850136676855</v>
+        <v>0.02487409420071236</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.0147977150899504</v>
+        <v>-0.01423860279428353</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.009821271636831955</v>
+        <v>-0.04785866803377671</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.01629809714187399</v>
+        <v>0.04568417559624435</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,25 +7675,25 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.006393810370857008</v>
+        <v>-0.00209243154610334</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.02114707821312171</v>
+        <v>0.02076504359517201</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.02266826729597521</v>
+        <v>-0.0004721479339982433</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,25 +7702,25 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.004161226869851361</v>
+        <v>-0.03003212525315077</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.04987443443258149</v>
+        <v>0.04794612033161379</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.03212969705020352</v>
+        <v>-0.04912614702417945</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,79 +7729,79 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.002067083161612181</v>
+        <v>0.0142158950499635</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.03586987147657198</v>
+        <v>0.04564397801994153</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.009966807537844621</v>
+        <v>-0.04164087739508616</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.02450720255252277</v>
+        <v>0.02213935109442886</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02007016203650738</v>
+        <v>0.03206456859147171</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01656175611585526</v>
+        <v>-0.008392559817458968</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.03254786776468042</v>
+        <v>-0.06363428363399139</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.001910338220346582</v>
+        <v>0.003337618630870601</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
         <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.03185289017775226</v>
+        <v>0.008461577814808607</v>
       </c>
       <c r="GA13" t="n">
         <v>-0</v>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.02516801095259726</v>
+        <v>-0.0156665054035929</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7833,25 +7833,25 @@
         <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.2713920259047215</v>
+        <v>-0.2920974386208073</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4674887659434525</v>
+        <v>0.1537107940647464</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1717145474556389</v>
+        <v>-0.06436824913015186</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -7860,40 +7860,40 @@
         <v>-0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1543278094167999</v>
+        <v>-0.1701526086703879</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4350887691328247</v>
+        <v>0.1101105023432042</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03413369257045911</v>
+        <v>0.03746552647196779</v>
       </c>
       <c r="O14" t="n">
         <v>-0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R14" t="n">
         <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
         <v>-0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.03695566141732533</v>
+        <v>-0.07480260195374351</v>
       </c>
       <c r="V14" t="n">
-        <v>0.09320280957839773</v>
+        <v>0.1579440208048382</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0462567315673718</v>
+        <v>0.06630226781786783</v>
       </c>
       <c r="X14" t="n">
         <v>-0</v>
@@ -7902,7 +7902,7 @@
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -7914,19 +7914,19 @@
         <v>-0</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.01263845319825641</v>
+        <v>-0.008118830131167083</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.03076335599084249</v>
+        <v>-0.1952540446953915</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.06678958734287736</v>
+        <v>-0.1547409473588657</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>-0</v>
@@ -7935,25 +7935,25 @@
         <v>-0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.01800484437191826</v>
+        <v>-0.08916980233392938</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.01499203002036055</v>
+        <v>0.1149454177966238</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0537903693884412</v>
+        <v>0.06167778621222255</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -7962,19 +7962,19 @@
         <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.1203890799250995</v>
+        <v>-0.1867798369269406</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.2775424142695002</v>
+        <v>0.2954810450035511</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.2146596411310845</v>
+        <v>-0.1155717887749743</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -7986,22 +7986,22 @@
         <v>-0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.04714373892103316</v>
+        <v>-0.007050729843892237</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.1124841055558299</v>
+        <v>-0.3341175806392999</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.1398744445589299</v>
+        <v>-0.1245983776512492</v>
       </c>
       <c r="BH14" t="n">
         <v>-0</v>
@@ -8010,163 +8010,163 @@
         <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>-0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0523973278937858</v>
+        <v>0.09495175184390255</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.03554094209032531</v>
+        <v>0.01993832531633147</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.2354941519274024</v>
+        <v>0.1711190072005028</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0.09909910004157414</v>
+        <v>-0.1921734473883518</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.1735016804746111</v>
+        <v>0.4721640941074394</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.1384560249384326</v>
+        <v>0.01589007403913517</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.09310089886401426</v>
+        <v>0.1161934694041345</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.09428287647893195</v>
+        <v>-0.03650945935213955</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.0161010829557872</v>
+        <v>0.005871304872802589</v>
       </c>
       <c r="CI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
         <v>-0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.01055555172610987</v>
+        <v>0.04363821418722977</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.0097995213366063</v>
+        <v>0.003113700016225753</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.1259013266618462</v>
+        <v>0.09980917211490792</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
         <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.05888633898892797</v>
+        <v>0.09294691942542754</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.07375734259386021</v>
+        <v>-0.03637794652294243</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.03720316251056358</v>
+        <v>0.02720045597055595</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0.003103298142165385</v>
+        <v>0.03983293230874226</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.09418537837694557</v>
+        <v>-0.08682687090652536</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.01319673520542707</v>
+        <v>-0.01524089351563583</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8178,19 +8178,19 @@
         <v>-0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.08982966660538205</v>
+        <v>0.006709044461044414</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0.03760661729374697</v>
+        <v>-0.04746812833725485</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.05321026511402761</v>
+        <v>0.09336440122335136</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
@@ -8205,31 +8205,31 @@
         <v>-0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX14" t="n">
         <v>-0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.03983219013552468</v>
+        <v>0.01857857876631081</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.04292437703844095</v>
+        <v>-0.005096599607415197</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.02350830427375013</v>
+        <v>-0.1671696853484622</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF14" t="n">
         <v>-0</v>
@@ -8238,22 +8238,22 @@
         <v>0</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.1153293570571029</v>
+        <v>0.06425792499222922</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.1192780297744908</v>
+        <v>0.08853635560219938</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.03604232929785856</v>
+        <v>-0.05431599981214429</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>0</v>
@@ -8262,55 +8262,55 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.07730050945238631</v>
+        <v>0.02984299221056263</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.06852533128791101</v>
+        <v>-0.09219111183062094</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.02150484559921831</v>
+        <v>-0.03087306504333693</v>
       </c>
       <c r="ET14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
         <v>-0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
         <v>0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.07909320403952123</v>
+        <v>0.1034824327058189</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.0849750051170132</v>
+        <v>-0.07202477685613461</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.023496901078208</v>
+        <v>0.02034323179220354</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
         <v>-0</v>
@@ -8319,19 +8319,19 @@
         <v>0</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.01536016367929654</v>
+        <v>0.1996803095129471</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.07522175049774142</v>
+        <v>-0.09964904500637542</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.08798364181380684</v>
+        <v>-0.1957204433336254</v>
       </c>
       <c r="FL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
         <v>-0</v>
@@ -8340,28 +8340,28 @@
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.01193308486977617</v>
+        <v>0.006192188214548633</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.01077138643607506</v>
+        <v>0.009744185887063628</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.06561818617602681</v>
+        <v>0.1236832521899815</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
@@ -8370,28 +8370,28 @@
         <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.06889672824767992</v>
+        <v>0.0881535080902848</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0233508787178196</v>
+        <v>-0.08687541828063423</v>
       </c>
       <c r="GC14" t="n">
         <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -8968,46 +8968,46 @@
         <v>-0</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.7003144703240248</v>
+        <v>-0.3763158604554189</v>
       </c>
       <c r="C16" t="n">
         <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.205655656289811</v>
+        <v>0.1080141391846401</v>
       </c>
       <c r="F16" t="n">
-        <v>1.026140977944456</v>
+        <v>0.5546883204510283</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.53218311405264</v>
+        <v>-0.4244848803014127</v>
       </c>
       <c r="L16" t="n">
         <v>-0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.04699799899504787</v>
+        <v>0.3020563847722151</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8844704594660923</v>
+        <v>0.5531257601359224</v>
       </c>
       <c r="P16" t="n">
         <v>-0</v>
@@ -9016,13 +9016,13 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.04194352853802243</v>
+        <v>-0.1328820297918179</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
@@ -9031,37 +9031,37 @@
         <v>-0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1336960578225319</v>
+        <v>0.1591727585895424</v>
       </c>
       <c r="X16" t="n">
-        <v>0.05198401444932234</v>
+        <v>0.07463508423253692</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.07054025168881072</v>
+        <v>-0.02074293331063401</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.02152473731719925</v>
+        <v>0.2724192447714864</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.03527858952691146</v>
+        <v>0.177958715038015</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
@@ -9070,67 +9070,67 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.08033701870268153</v>
+        <v>-0.1362826376378882</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN16" t="n">
         <v>-0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.02339251278766288</v>
+        <v>-0.06278974348702805</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.1411806023768922</v>
+        <v>0.138474158284885</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0.3896558316644269</v>
+        <v>-0.5369607644488481</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1824017199011367</v>
+        <v>0.1275537172683595</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.5680457729559656</v>
+        <v>0.3179149934108095</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>-0.2644471257703686</v>
+        <v>0.08773267130409113</v>
       </c>
       <c r="BE16" t="n">
         <v>-0</v>
@@ -9139,10 +9139,10 @@
         <v>-0</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.1115468654359296</v>
+        <v>0.2005009272158735</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.2356819412487435</v>
+        <v>0.112746307415037</v>
       </c>
       <c r="BI16" t="n">
         <v>-0</v>
@@ -9154,25 +9154,25 @@
         <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0.2266396987214865</v>
+        <v>-0.06960742287914121</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>-0.08854685889052873</v>
+        <v>-0.157340729295455</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.02192399888022407</v>
+        <v>-0.0004956035986791356</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
@@ -9181,52 +9181,52 @@
         <v>-0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>-0.2836484257586062</v>
+        <v>-0.3855700875748046</v>
       </c>
       <c r="BW16" t="n">
         <v>-0</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.04710402786634522</v>
+        <v>0.1059758938056528</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.2954565879739654</v>
+        <v>0.2326526023957651</v>
       </c>
       <c r="CA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="n">
         <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
         <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.1357974999377761</v>
+        <v>0.1360277628193169</v>
       </c>
       <c r="CF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.03618657728704906</v>
+        <v>-0.02551918049643501</v>
       </c>
       <c r="CI16" t="n">
-        <v>-0.1722295822184476</v>
+        <v>-0.1374393139109585</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK16" t="n">
         <v>-0</v>
@@ -9238,61 +9238,61 @@
         <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.07038093452237335</v>
+        <v>0.271803917662829</v>
       </c>
       <c r="CO16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP16" t="n">
         <v>0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.1216231826030716</v>
+        <v>-0.196700145587344</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.05019988756528392</v>
+        <v>-0.1352908610718352</v>
       </c>
       <c r="CS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT16" t="n">
         <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.1051953402666872</v>
+        <v>0.09585904909154037</v>
       </c>
       <c r="CX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.03265290375986804</v>
+        <v>-0.03301353707836732</v>
       </c>
       <c r="DA16" t="n">
-        <v>-0.1610522528340039</v>
+        <v>-0.1513279787716155</v>
       </c>
       <c r="DB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC16" t="n">
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.0476490491710258</v>
+        <v>0.1208610566917738</v>
       </c>
       <c r="DG16" t="n">
         <v>0</v>
@@ -9301,43 +9301,43 @@
         <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.1570659987051416</v>
+        <v>0.1620319132659268</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.00977342687967179</v>
+        <v>-0.05051658856286744</v>
       </c>
       <c r="DK16" t="n">
         <v>-0</v>
       </c>
       <c r="DL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN16" t="n">
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.04655919104029107</v>
+        <v>-0.02728467591851239</v>
       </c>
       <c r="DP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ16" t="n">
         <v>-0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.008537785173568454</v>
+        <v>0.1046705593657865</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.08513490918137259</v>
+        <v>-0.06108212727488813</v>
       </c>
       <c r="DT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
@@ -9346,103 +9346,103 @@
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.01485170521057556</v>
+        <v>-0.1488465353548438</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.06411952547542912</v>
+        <v>0.001267429969933861</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0.05525078674026609</v>
+        <v>-0.08834468816434597</v>
       </c>
       <c r="EC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.1206035740851972</v>
+        <v>0.02674802746417302</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI16" t="n">
         <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>-0.08167537952083161</v>
+        <v>-0.01283877194094561</v>
       </c>
       <c r="EK16" t="n">
-        <v>-0.1523629843260345</v>
+        <v>-0.03958636952913908</v>
       </c>
       <c r="EL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM16" t="n">
         <v>0</v>
       </c>
       <c r="EN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.04392153538909991</v>
+        <v>0.05110658939113159</v>
       </c>
       <c r="EQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.09174754941895624</v>
+        <v>0.03986652710772733</v>
       </c>
       <c r="ET16" t="n">
-        <v>-0.02327583101063512</v>
+        <v>-0.2142259745708726</v>
       </c>
       <c r="EU16" t="n">
         <v>0</v>
       </c>
       <c r="EV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.09655867996757575</v>
+        <v>0.1589526390353068</v>
       </c>
       <c r="EZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA16" t="n">
         <v>0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.05901205289109376</v>
+        <v>-0.005515511987697142</v>
       </c>
       <c r="FC16" t="n">
-        <v>-0.1667056595649672</v>
+        <v>-0.1453811747045665</v>
       </c>
       <c r="FD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE16" t="n">
         <v>-0</v>
@@ -9454,61 +9454,61 @@
         <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.06588430176579278</v>
+        <v>0.1274923375991713</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.0279240643535699</v>
+        <v>-0.1059137452034941</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0.1354326642533302</v>
+        <v>-0.1344136745025702</v>
       </c>
       <c r="FM16" t="n">
         <v>-0</v>
       </c>
       <c r="FN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO16" t="n">
         <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.002282058275549137</v>
+        <v>-0.001105904806268982</v>
       </c>
       <c r="FR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS16" t="n">
         <v>0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.02152876426235856</v>
+        <v>0.03734783214664512</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0.1304117943092</v>
+        <v>-0.07367743185673462</v>
       </c>
       <c r="FV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX16" t="n">
         <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.03443915957421868</v>
+        <v>0.04757569233216155</v>
       </c>
       <c r="GA16" t="n">
         <v>-0</v>
@@ -9517,16 +9517,16 @@
         <v>0</v>
       </c>
       <c r="GC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.1056542476631123</v>
+        <v>-0.00373573344233456</v>
       </c>
       <c r="GE16" t="n">
         <v>0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
         <v>-0</v>
